--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20221.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20221.xlsx
@@ -629,10 +629,10 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>21</v>
@@ -641,7 +641,7 @@
         <v>61.76</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -798,7 +798,7 @@
         <v>34</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -952,10 +952,10 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>21</v>
@@ -964,7 +964,7 @@
         <v>61.76</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20221.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="29">
   <si>
     <t>Mat</t>
   </si>
@@ -79,49 +79,16 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
     <t>MOLINA</t>
   </si>
   <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
     <t>TETLA</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
+    <t>TIZA</t>
   </si>
   <si>
     <t>DE JESUS</t>
@@ -130,79 +97,13 @@
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>FELIPE</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CRISTOBAL</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
+    <t>CRISTIAN OSMAR</t>
   </si>
   <si>
     <t>VICTOR MANUEL</t>
   </si>
   <si>
-    <t>ABDIEL NOE</t>
-  </si>
-  <si>
     <t>LUIS</t>
-  </si>
-  <si>
-    <t>NAHUM HIRAM</t>
-  </si>
-  <si>
-    <t>VALERIA DANAY</t>
-  </si>
-  <si>
-    <t>ELIDA CITLALI</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>MIRIAM AIMAR</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
-  </si>
-  <si>
-    <t>TRISTAN YABAL</t>
-  </si>
-  <si>
-    <t>JOSUE GUSTAVO</t>
-  </si>
-  <si>
-    <t>KARLA YARITZY</t>
-  </si>
-  <si>
-    <t>JESUS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>MICHELLE</t>
   </si>
 </sst>
 </file>
@@ -603,19 +504,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>58.97</v>
+        <v>82.05</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -629,19 +530,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>61.76</v>
+        <v>97.06</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -655,19 +556,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G4">
-        <v>75.61</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -678,22 +579,22 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G5">
-        <v>78.05</v>
+        <v>90</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -707,19 +608,19 @@
         <v>36</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G6">
-        <v>91.67</v>
+        <v>97.22</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -772,16 +673,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>82.05</v>
+      </c>
+      <c r="H2">
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -795,16 +699,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>94.12</v>
+      </c>
+      <c r="H3">
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -821,7 +728,7 @@
         <v>41</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -838,19 +745,22 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E5">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H5">
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -864,16 +774,19 @@
         <v>36</v>
       </c>
       <c r="D6">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>97.22</v>
+      </c>
+      <c r="H6">
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -926,19 +839,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>58.97</v>
+        <v>82.05</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -952,19 +865,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>61.76</v>
+        <v>94.12</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -978,19 +891,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G4">
-        <v>75.61</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1001,19 +914,19 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>78.05</v>
+        <v>87.5</v>
       </c>
       <c r="H5">
         <v>8</v>
@@ -1030,19 +943,19 @@
         <v>36</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G6">
-        <v>91.67</v>
+        <v>97.22</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1052,7 +965,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1084,16 +997,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920193</v>
+        <v>22330051920359</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1107,16 +1020,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920180</v>
+        <v>22330051920193</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
         <v>27</v>
-      </c>
-      <c r="D3" t="s">
-        <v>48</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1136,10 +1049,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1149,282 +1062,6 @@
       </c>
       <c r="G4">
         <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920200</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920216</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920420</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920281</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920303</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920370</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920397</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920196</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920356</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920374</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920317</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920224</v>
-      </c>
-      <c r="B16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20221.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="26">
   <si>
     <t>Mat</t>
   </si>
@@ -79,25 +79,16 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
     <t>MOLINA</t>
   </si>
   <si>
     <t>TETLA</t>
   </si>
   <si>
-    <t>TIZA</t>
-  </si>
-  <si>
     <t>DE JESUS</t>
   </si>
   <si>
     <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>CRISTIAN OSMAR</t>
   </si>
   <si>
     <t>VICTOR MANUEL</t>
@@ -965,7 +956,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -997,16 +988,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920359</v>
+        <v>22330051920193</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1020,16 +1011,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920193</v>
+        <v>22330051920390</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1038,29 +1029,6 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920390</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20221.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20221.xlsx
@@ -716,16 +716,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>85.37</v>
+      </c>
+      <c r="H4">
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -739,19 +742,19 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G5">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -885,13 +888,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G4">
-        <v>90.23999999999999</v>
+        <v>85.37</v>
       </c>
       <c r="H4">
         <v>7.8</v>
@@ -911,16 +914,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G5">
-        <v>87.5</v>
+        <v>85</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20221.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="32">
   <si>
     <t>Mat</t>
   </si>
@@ -79,22 +79,40 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
     <t>MOLINA</t>
   </si>
   <si>
-    <t>TETLA</t>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>TIZA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
   </si>
   <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
+    <t>FABIAN ALEJANDRO</t>
+  </si>
+  <si>
+    <t>CRISTIAN OSMAR</t>
+  </si>
+  <si>
+    <t>LUIS</t>
   </si>
   <si>
     <t>VICTOR MANUEL</t>
-  </si>
-  <si>
-    <t>LUIS</t>
   </si>
 </sst>
 </file>
@@ -959,7 +977,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -991,16 +1009,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920193</v>
+        <v>22330051920413</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1014,16 +1032,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920390</v>
+        <v>22330051920359</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1033,6 +1051,52 @@
       </c>
       <c r="G3">
         <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>22330051920390</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330051920193</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20221.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="20">
   <si>
     <t>Mat</t>
   </si>
@@ -77,42 +77,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>TIZA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>FABIAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>CRISTIAN OSMAR</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>VICTOR MANUEL</t>
   </si>
 </sst>
 </file>
@@ -854,16 +818,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G2">
-        <v>82.05</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -880,16 +844,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -932,16 +896,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G5">
-        <v>85</v>
+        <v>97.5</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -958,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G6">
-        <v>97.22</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>8</v>
@@ -977,7 +941,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1007,98 +971,6 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920413</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920359</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920390</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920193</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20221.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20221.xlsx
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G4">
-        <v>85.37</v>
+        <v>95.12</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
